--- a/Export from PAD Portal.xlsx
+++ b/Export from PAD Portal.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cigpsa-my.sharepoint.com/personal/kate_zhang_cigp_com/Documents/Desktop/PAD Automation/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="14" documentId="11_0A9891C2DD619A4A700528AE256CAFD37D660B09" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9C4B207E-BD5D-4544-B134-9B9CA76B5F2A}"/>
+  <xr:revisionPtr revIDLastSave="17" documentId="11_0A9891C2DD619A4A700528AE256CAFD37D660B09" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C1AFE6D2-1B3F-4716-8BDF-DD68F0A011C4}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView minimized="1" xWindow="5400" yWindow="2460" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$F$83</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$A$83</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -854,7 +854,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr>
+  <sheetPr filterMode="1">
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:F83"/>
@@ -888,7 +888,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>6</v>
       </c>
@@ -908,7 +908,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>10</v>
       </c>
@@ -928,7 +928,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>10</v>
       </c>
@@ -948,7 +948,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>15</v>
       </c>
@@ -968,7 +968,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>17</v>
       </c>
@@ -988,7 +988,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>20</v>
       </c>
@@ -1008,7 +1008,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>23</v>
       </c>
@@ -1028,7 +1028,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>23</v>
       </c>
@@ -1048,7 +1048,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>23</v>
       </c>
@@ -1068,7 +1068,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>23</v>
       </c>
@@ -1088,7 +1088,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>20</v>
       </c>
@@ -1108,7 +1108,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>20</v>
       </c>
@@ -1128,7 +1128,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>23</v>
       </c>
@@ -1148,7 +1148,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>23</v>
       </c>
@@ -1168,7 +1168,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
         <v>23</v>
       </c>
@@ -1188,7 +1188,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
         <v>23</v>
       </c>
@@ -1228,7 +1228,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
         <v>10</v>
       </c>
@@ -1288,7 +1288,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
         <v>6</v>
       </c>
@@ -1308,7 +1308,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
         <v>6</v>
       </c>
@@ -1348,7 +1348,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
         <v>6</v>
       </c>
@@ -1368,7 +1368,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
         <v>46</v>
       </c>
@@ -1408,7 +1408,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
         <v>51</v>
       </c>
@@ -1428,7 +1428,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
         <v>51</v>
       </c>
@@ -1468,7 +1468,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
         <v>23</v>
       </c>
@@ -1488,7 +1488,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
         <v>23</v>
       </c>
@@ -1528,7 +1528,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
         <v>46</v>
       </c>
@@ -1608,7 +1608,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
         <v>46</v>
       </c>
@@ -1668,7 +1668,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
         <v>15</v>
       </c>
@@ -1708,7 +1708,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
         <v>72</v>
       </c>
@@ -1828,7 +1828,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
         <v>81</v>
       </c>
@@ -1848,7 +1848,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
         <v>81</v>
       </c>
@@ -1868,7 +1868,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
         <v>81</v>
       </c>
@@ -1888,7 +1888,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
         <v>81</v>
       </c>
@@ -1908,7 +1908,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
         <v>81</v>
       </c>
@@ -1928,7 +1928,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
         <v>6</v>
       </c>
@@ -2008,7 +2008,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
         <v>92</v>
       </c>
@@ -2028,7 +2028,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="s">
         <v>6</v>
       </c>
@@ -2048,7 +2048,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
         <v>6</v>
       </c>
@@ -2068,7 +2068,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A61" s="2" t="s">
         <v>15</v>
       </c>
@@ -2088,7 +2088,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="s">
         <v>6</v>
       </c>
@@ -2108,7 +2108,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A63" s="2" t="s">
         <v>20</v>
       </c>
@@ -2128,7 +2128,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="s">
         <v>92</v>
       </c>
@@ -2148,7 +2148,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A65" s="2" t="s">
         <v>92</v>
       </c>
@@ -2168,7 +2168,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A66" s="2" t="s">
         <v>102</v>
       </c>
@@ -2188,7 +2188,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A67" s="2" t="s">
         <v>46</v>
       </c>
@@ -2208,7 +2208,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A68" s="2" t="s">
         <v>72</v>
       </c>
@@ -2228,7 +2228,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A69" s="2" t="s">
         <v>72</v>
       </c>
@@ -2248,7 +2248,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A70" s="2" t="s">
         <v>102</v>
       </c>
@@ -2308,7 +2308,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A73" s="2" t="s">
         <v>6</v>
       </c>
@@ -2328,7 +2328,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A74" s="2" t="s">
         <v>6</v>
       </c>
@@ -2348,7 +2348,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A75" s="2" t="s">
         <v>6</v>
       </c>
@@ -2368,7 +2368,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A76" s="2" t="s">
         <v>114</v>
       </c>
@@ -2388,7 +2388,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A77" s="2" t="s">
         <v>20</v>
       </c>
@@ -2468,7 +2468,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A81" s="2" t="s">
         <v>6</v>
       </c>
@@ -2488,7 +2488,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A82" s="2" t="s">
         <v>102</v>
       </c>
@@ -2508,7 +2508,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A83" s="2" t="s">
         <v>102</v>
       </c>
@@ -2529,7 +2529,13 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F83" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:A83" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <filterColumn colId="0">
+      <filters>
+        <filter val="Alberto Pasini"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter alignWithMargins="0">
     <oddFooter>&amp;L_x000D_&amp;1#&amp;"Aptos"&amp;12&amp;K000000 INTERNAL</oddFooter>
@@ -2538,32 +2544,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <Tag xmlns="84ebf1d2-7948-493c-8c62-2ca8e383162c" xsi:nil="true"/>
-    <FirstRound xmlns="84ebf1d2-7948-493c-8c62-2ca8e383162c">true</FirstRound>
-    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <TaxCatchAll xmlns="742899a5-620b-46b4-8028-e0b32381c729" xsi:nil="true"/>
-    <DocumentType xmlns="84ebf1d2-7948-493c-8c62-2ca8e383162c" xsi:nil="true"/>
-    <DateofCertification xmlns="84ebf1d2-7948-493c-8c62-2ca8e383162c" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="84ebf1d2-7948-493c-8c62-2ca8e383162c">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100252F1BFCADBC0848A5FED0D06D89763B" ma:contentTypeVersion="25" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="68f0e11f74df8d300ee4193468ab27a0">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="742899a5-620b-46b4-8028-e0b32381c729" xmlns:ns3="84ebf1d2-7948-493c-8c62-2ca8e383162c" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="9f3425df69acaae048487c9f62322dd7" ns1:_="" ns2:_="" ns3:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
@@ -2873,27 +2853,33 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7D5CEAB2-0A9C-4FB4-B5BB-6E6CD11D10DE}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
-    <ds:schemaRef ds:uri="84ebf1d2-7948-493c-8c62-2ca8e383162c"/>
-    <ds:schemaRef ds:uri="742899a5-620b-46b4-8028-e0b32381c729"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <Tag xmlns="84ebf1d2-7948-493c-8c62-2ca8e383162c" xsi:nil="true"/>
+    <FirstRound xmlns="84ebf1d2-7948-493c-8c62-2ca8e383162c">true</FirstRound>
+    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <TaxCatchAll xmlns="742899a5-620b-46b4-8028-e0b32381c729" xsi:nil="true"/>
+    <DocumentType xmlns="84ebf1d2-7948-493c-8c62-2ca8e383162c" xsi:nil="true"/>
+    <DateofCertification xmlns="84ebf1d2-7948-493c-8c62-2ca8e383162c" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="84ebf1d2-7948-493c-8c62-2ca8e383162c">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{51DA29CD-F16A-4707-B45C-2732F7034169}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AC668AF1-87ED-483C-9676-EDD61ECC2E41}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -2911,4 +2897,24 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7D5CEAB2-0A9C-4FB4-B5BB-6E6CD11D10DE}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
+    <ds:schemaRef ds:uri="84ebf1d2-7948-493c-8c62-2ca8e383162c"/>
+    <ds:schemaRef ds:uri="742899a5-620b-46b4-8028-e0b32381c729"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{51DA29CD-F16A-4707-B45C-2732F7034169}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>